--- a/Manual-Testing/TestCases.xlsx
+++ b/Manual-Testing/TestCases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BLESSY B SHERIN\OneDrive\Desktop\QA-Portfolio\Manual-Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{B44E15A8-79AF-4314-B349-6733CEDDB442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{904F3CBE-392B-4F0C-BDCA-633E2EE12C1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{50DBE3AA-95EE-4A47-847B-B904F86F9350}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>

--- a/Manual-Testing/TestCases.xlsx
+++ b/Manual-Testing/TestCases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BLESSY B SHERIN\OneDrive\Desktop\QA-Portfolio\Manual-Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{904F3CBE-392B-4F0C-BDCA-633E2EE12C1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A98D3201-2843-4211-B813-B6AA3D094611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{50DBE3AA-95EE-4A47-847B-B904F86F9350}"/>
   </bookViews>
